--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.27537559171719</v>
+        <v>7.357248533654043</v>
       </c>
       <c r="D2" t="n">
-        <v>20.88659857420542</v>
+        <v>3.394072268308381</v>
       </c>
       <c r="E2" t="n">
-        <v>11.817812407051</v>
+        <v>1.920394516145788</v>
       </c>
       <c r="F2" t="n">
-        <v>13.16232468505049</v>
+        <v>2.138877761320705</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.38190270209986</v>
+        <v>4.449559189091228</v>
       </c>
       <c r="D3" t="n">
-        <v>43.18875542994107</v>
+        <v>7.018172757365424</v>
       </c>
       <c r="E3" t="n">
-        <v>11.817812407051</v>
+        <v>1.920394516145788</v>
       </c>
       <c r="F3" t="n">
-        <v>13.16232468505049</v>
+        <v>2.138877761320705</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.62077013859466</v>
+        <v>2.700875147521633</v>
       </c>
       <c r="D4" t="n">
-        <v>47.63467749444726</v>
+        <v>7.74063509284768</v>
       </c>
       <c r="E4" t="n">
-        <v>11.817812407051</v>
+        <v>1.920394516145788</v>
       </c>
       <c r="F4" t="n">
-        <v>13.16232468505049</v>
+        <v>2.138877761320705</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.57123755371802</v>
+        <v>4.317826102479179</v>
       </c>
       <c r="D5" t="n">
-        <v>12.56776854673337</v>
+        <v>2.042262388844173</v>
       </c>
       <c r="E5" t="n">
-        <v>11.817812407051</v>
+        <v>1.920394516145788</v>
       </c>
       <c r="F5" t="n">
-        <v>13.16232468505049</v>
+        <v>2.138877761320705</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.27368760187024</v>
+        <v>2.644474235303914</v>
       </c>
       <c r="D6" t="n">
-        <v>22.80669656401964</v>
+        <v>3.706088191653192</v>
       </c>
       <c r="E6" t="n">
-        <v>11.817812407051</v>
+        <v>1.920394516145788</v>
       </c>
       <c r="F6" t="n">
-        <v>13.16232468505049</v>
+        <v>2.138877761320705</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.98804082913094</v>
+        <v>4.385556634733778</v>
       </c>
       <c r="D7" t="n">
-        <v>25.87243988308823</v>
+        <v>4.204271481001838</v>
       </c>
       <c r="E7" t="n">
-        <v>11.817812407051</v>
+        <v>1.920394516145788</v>
       </c>
       <c r="F7" t="n">
-        <v>13.16232468505049</v>
+        <v>2.138877761320705</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.93291872698787</v>
+        <v>3.889099293135529</v>
       </c>
       <c r="D8" t="n">
-        <v>24.5946986443645</v>
+        <v>3.996638529709231</v>
       </c>
       <c r="E8" t="n">
-        <v>11.817812407051</v>
+        <v>1.920394516145788</v>
       </c>
       <c r="F8" t="n">
-        <v>13.16232468505049</v>
+        <v>2.138877761320705</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.35332749142893</v>
+        <v>8.344915717357202</v>
       </c>
       <c r="D9" t="n">
-        <v>50.60155565051764</v>
+        <v>8.222752793209116</v>
       </c>
       <c r="E9" t="n">
-        <v>11.817812407051</v>
+        <v>1.920394516145788</v>
       </c>
       <c r="F9" t="n">
-        <v>13.16232468505049</v>
+        <v>2.138877761320705</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
